--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T07:22:41+00:00</t>
+    <t>2026-09-24T12:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -640,7 +640,7 @@
     <t>**AutorSpecialty**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260505120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260730120000</t>
   </si>
   <si>
     <t>AuthorDocumentEntry</t>
@@ -801,7 +801,7 @@
     <t>Identifiant unique affecté à la version de la fiche référençant le document.</t>
   </si>
   <si>
-    <t>Les valeurs possibles pour cette métadonnée doivent être un code provenant du jeu de valeurs mis à disposition par le projet. En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J52_AvailabilityStatus_CISIS peut être utilisé.</t>
+    <t>Cet identifiant est attribué par le registre du système cible lors de la soumission. Il change à chaque nouvelle version de la fiche, à la différence de logicalId qui reste invariable.</t>
   </si>
   <si>
     <t>DocumentEntry.logicalId</t>
